--- a/public/templates/workload-report.xlsx
+++ b/public/templates/workload-report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\var\www\platform_next\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECBB4D5-ADF0-4029-A769-4AB41B78FAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448F4633-B149-4286-90D9-86CEF3D8E3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{2CA2DA6A-04EF-4635-8A28-80210C2BCD2E}"/>
   </bookViews>
@@ -176,16 +176,18 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">                          </t>
+      <t xml:space="preserve">                            </t>
     </r>
     <r>
       <rPr>
         <u/>
         <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  YYYY  </t>
+      <t xml:space="preserve"> YYYY </t>
     </r>
     <r>
       <rPr>
@@ -203,16 +205,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>　YYYY</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="14"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve"> YYYY </t>
     </r>
     <r>
       <rPr>
@@ -313,7 +306,7 @@
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="178" formatCode="0.0_);[Red]\(0.0\)"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -397,6 +390,14 @@
       <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
